--- a/Unterlagen/Stueckliste_RevE_20260929.xlsx
+++ b/Unterlagen/Stueckliste_RevE_20260929.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mbmicrotec-my.sharepoint.com/personal/markus_dietschi_mbmicrotec_com/Documents/_DIM_Privat/_Software/Huehnerstall_20260929/Stuecklisten/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_DIM\_GitHubRepository\ChickenGateSystem\Unterlagen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1070" documentId="13_ncr:1_{D63D705F-4428-47D5-A626-A13F6BC1B6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97568E74-735D-4EB0-9792-C92DBF176653}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315754E0-5574-4A94-84BE-B6C92B608102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,8 @@
     <sheet name="Stückliste" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_A100000">Stückliste!$A$9508</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Stückliste!$A$5:$J$71</definedName>
+    <definedName name="_A100000">Stückliste!$A$9505</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Stückliste!$A$5:$J$68</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="241">
   <si>
     <t>Art.-Nr.</t>
   </si>
@@ -294,9 +294,6 @@
     <t>301-01-974</t>
   </si>
   <si>
-    <t xml:space="preserve">  Zenerdiode 4,7V</t>
-  </si>
-  <si>
     <t>Relais / 2-Wechsler / Bistabil / 2-Spulen / 12VDC</t>
   </si>
   <si>
@@ -375,9 +372,6 @@
     <t>VISHAY</t>
   </si>
   <si>
-    <t>BZX55C4V7-TAP</t>
-  </si>
-  <si>
     <t xml:space="preserve">  MOSFET zur Relaissteuerung</t>
   </si>
   <si>
@@ -624,12 +618,6 @@
     <t xml:space="preserve">  Zenerdiode 5,1V</t>
   </si>
   <si>
-    <t>Zener-Diode, 4.7 V, 500 mW, DO-35, ± 5%-Tolerance</t>
-  </si>
-  <si>
-    <t>78-BZX55C4V7-TAP</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Zenerdiode 4,7V - Alternative</t>
   </si>
   <si>
@@ -711,24 +699,12 @@
     <t>Kleinsignaldiode, 100 V, 1A, DO-35</t>
   </si>
   <si>
-    <t>1N5817</t>
-  </si>
-  <si>
-    <t>Kleinsignaldiode, 20 V, 1A, DO-15</t>
-  </si>
-  <si>
-    <t>637-1N5817</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Sperrdiode 100V   -   als Freilaufdiode</t>
   </si>
   <si>
     <t xml:space="preserve">  Sperrdiode 75V   -   für Sammelinterrupt</t>
   </si>
   <si>
-    <t xml:space="preserve">  Sperrdiode 20V   -   FDTI-Adapter Rückspeisung</t>
-  </si>
-  <si>
     <t>LDR-Lichtabhängiger Widerstand   (identisch)</t>
   </si>
   <si>
@@ -772,6 +748,15 @@
   </si>
   <si>
     <t>594-MBB02070C4701FCT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Widerstand 4.7 kOhm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Widerstand 220 Ohm</t>
+  </si>
+  <si>
+    <t>Widerstand, 600mW, 330 Ohm, 1 %</t>
   </si>
 </sst>
 </file>
@@ -863,7 +848,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1045,37 +1030,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1084,7 +1038,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1137,24 +1091,9 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1162,9 +1101,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1222,10 +1158,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1346,10 +1278,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1642,7 +1570,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:K71"/>
+  <dimension ref="A2:K68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.1" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51.28515625" style="1" customWidth="1"/>
@@ -1652,72 +1580,72 @@
     <col min="5" max="5" width="87.85546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.28515625" style="1" customWidth="1"/>
     <col min="7" max="7" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="15" style="25" customWidth="1"/>
+    <col min="8" max="9" width="15" style="20" customWidth="1"/>
     <col min="10" max="10" width="12.85546875" style="1" customWidth="1"/>
     <col min="11" max="11" width="2.42578125" style="1" customWidth="1"/>
     <col min="12" max="16384" width="0" style="1" hidden="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
+      <c r="A2" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
     </row>
     <row r="5" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="73" t="s">
+      <c r="B5" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="73" t="s">
+      <c r="C5" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="73" t="s">
+      <c r="D5" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="73" t="s">
+      <c r="E5" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="73" t="s">
+      <c r="F5" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="78" t="s">
+      <c r="G5" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="H5" s="76" t="s">
+      <c r="H5" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="76" t="s">
+      <c r="I5" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="73" t="s">
+      <c r="J5" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="K5" s="75"/>
+      <c r="K5" s="67"/>
     </row>
     <row r="6" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="74"/>
-      <c r="B6" s="74"/>
-      <c r="C6" s="74"/>
-      <c r="D6" s="74"/>
-      <c r="E6" s="74"/>
-      <c r="F6" s="74"/>
-      <c r="G6" s="79"/>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
-      <c r="J6" s="74"/>
-      <c r="K6" s="75"/>
+      <c r="A6" s="66"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="67"/>
     </row>
     <row r="7" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
@@ -1727,8 +1655,8 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
       <c r="J7" s="4"/>
       <c r="K7" s="2"/>
     </row>
@@ -1744,29 +1672,29 @@
       <c r="A9" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="51" t="s">
+      <c r="B9" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="52" t="s">
+      <c r="D9" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="53" t="s">
+      <c r="E9" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="51" t="s">
+      <c r="F9" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="52" t="s">
+      <c r="G9" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="44">
+      <c r="H9" s="38">
         <v>50</v>
       </c>
-      <c r="I9" s="63">
-        <f t="shared" ref="I9:I68" si="0">J9*H9</f>
+      <c r="I9" s="55">
+        <f t="shared" ref="I9:I66" si="0">J9*H9</f>
         <v>50</v>
       </c>
       <c r="J9" s="8">
@@ -1777,28 +1705,28 @@
       <c r="A10" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="46" t="s">
+      <c r="B10" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="45" t="s">
+      <c r="D10" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="54" t="s">
+      <c r="E10" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="46" t="s">
+      <c r="F10" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="45" t="s">
+      <c r="G10" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="44">
+      <c r="H10" s="38">
         <v>10</v>
       </c>
-      <c r="I10" s="63">
+      <c r="I10" s="55">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -1807,31 +1735,31 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="68" t="s">
+      <c r="A11" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="56" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="57" t="s">
+      <c r="B11" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="66" t="s">
+      <c r="D11" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="69" t="s">
+      <c r="E11" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="57" t="s">
+      <c r="F11" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="66" t="s">
+      <c r="G11" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="70">
+      <c r="H11" s="62">
         <v>10</v>
       </c>
-      <c r="I11" s="62">
+      <c r="I11" s="54">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1843,26 +1771,26 @@
       <c r="A12" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="46" t="s">
+      <c r="B12" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="46"/>
-      <c r="E12" s="54" t="s">
+      <c r="D12" s="40"/>
+      <c r="E12" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="46" t="s">
+      <c r="F12" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="G12" s="55" t="s">
+      <c r="G12" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="44">
+      <c r="H12" s="38">
         <v>0.8</v>
       </c>
-      <c r="I12" s="63">
+      <c r="I12" s="55">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1871,43 +1799,43 @@
       </c>
     </row>
     <row r="13" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="47"/>
+      <c r="A13" s="41"/>
       <c r="B13" s="14"/>
       <c r="E13" s="12"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="26">
+      <c r="G13" s="24"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J13" s="10"/>
     </row>
     <row r="14" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="68" t="s">
+      <c r="A14" s="60" t="s">
         <v>75</v>
       </c>
-      <c r="B14" s="56" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="58" t="s">
+      <c r="B14" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="D14" s="58" t="s">
+      <c r="D14" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="E14" s="59" t="s">
-        <v>98</v>
-      </c>
-      <c r="F14" s="58" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14" s="64" t="s">
+      <c r="E14" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="F14" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="H14" s="65">
+      <c r="H14" s="57">
         <v>4.7</v>
       </c>
-      <c r="I14" s="62">
+      <c r="I14" s="54">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1917,30 +1845,30 @@
     </row>
     <row r="15" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>155</v>
+      </c>
+      <c r="E15" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="B15" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>156</v>
-      </c>
-      <c r="D15" s="38" t="s">
-        <v>157</v>
-      </c>
-      <c r="E15" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="F15" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" s="40" t="s">
-        <v>155</v>
-      </c>
-      <c r="H15" s="41">
+      <c r="F15" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="H15" s="35">
         <v>8.6</v>
       </c>
-      <c r="I15" s="63">
+      <c r="I15" s="55">
         <f t="shared" si="0"/>
         <v>8.6</v>
       </c>
@@ -1950,30 +1878,30 @@
     </row>
     <row r="16" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="B16" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="D16" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="B16" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" s="36" t="s">
         <v>110</v>
       </c>
-      <c r="E16" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="F16" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16" s="45" t="s">
-        <v>158</v>
-      </c>
-      <c r="H16" s="44">
+      <c r="F16" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="H16" s="38">
         <v>0.6</v>
       </c>
-      <c r="I16" s="63">
+      <c r="I16" s="55">
         <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
@@ -1983,30 +1911,30 @@
     </row>
     <row r="17" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="B17" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="D17" s="38" t="s">
-        <v>107</v>
-      </c>
-      <c r="E17" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="F17" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17" s="45" t="s">
-        <v>160</v>
-      </c>
-      <c r="H17" s="44">
+      <c r="F17" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="H17" s="38">
         <v>0.6</v>
       </c>
-      <c r="I17" s="63">
+      <c r="I17" s="55">
         <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
@@ -2016,30 +1944,30 @@
     </row>
     <row r="18" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="B18" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>105</v>
-      </c>
-      <c r="D18" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="E18" s="36" t="s">
         <v>169</v>
       </c>
-      <c r="E18" s="42" t="s">
-        <v>171</v>
-      </c>
-      <c r="F18" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18" s="45" t="s">
-        <v>170</v>
-      </c>
-      <c r="H18" s="44">
+      <c r="F18" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="39" t="s">
+        <v>168</v>
+      </c>
+      <c r="H18" s="38">
         <v>0.2</v>
       </c>
-      <c r="I18" s="63">
+      <c r="I18" s="55">
         <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
@@ -2049,30 +1977,30 @@
     </row>
     <row r="19" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="B19" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="38" t="s">
-        <v>167</v>
-      </c>
-      <c r="E19" s="71" t="s">
+      <c r="D19" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="E19" s="63" t="s">
+        <v>164</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="F19" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19" s="45" t="s">
-        <v>168</v>
-      </c>
-      <c r="H19" s="44">
+      <c r="H19" s="38">
         <v>0.4</v>
       </c>
-      <c r="I19" s="63">
+      <c r="I19" s="55">
         <f t="shared" si="0"/>
         <v>2.4000000000000004</v>
       </c>
@@ -2084,26 +2012,26 @@
       <c r="A20" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="B20" s="37"/>
-      <c r="C20" s="38" t="s">
+      <c r="B20" s="31"/>
+      <c r="C20" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="D20" s="38">
+      <c r="D20" s="32">
         <v>55900000001</v>
       </c>
-      <c r="E20" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="F20" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="H20" s="41">
+      <c r="E20" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="H20" s="35">
         <v>1</v>
       </c>
-      <c r="I20" s="63">
+      <c r="I20" s="55">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -2113,28 +2041,28 @@
     </row>
     <row r="21" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="B21" s="37"/>
-      <c r="C21" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" s="31"/>
+      <c r="C21" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="D21" s="38">
+      <c r="D21" s="32">
         <v>37212000411</v>
       </c>
-      <c r="E21" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="F21" s="38" t="s">
+      <c r="E21" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="F21" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="G21" s="40">
+      <c r="G21" s="34">
         <v>2786441</v>
       </c>
-      <c r="H21" s="41">
+      <c r="H21" s="35">
         <v>1</v>
       </c>
-      <c r="I21" s="63">
+      <c r="I21" s="55">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -2146,26 +2074,26 @@
       <c r="A22" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="B22" s="37"/>
-      <c r="C22" s="38" t="s">
+      <c r="B22" s="31"/>
+      <c r="C22" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="38">
+      <c r="D22" s="32">
         <v>37005000430</v>
       </c>
-      <c r="E22" s="39" t="s">
-        <v>118</v>
-      </c>
-      <c r="F22" s="38" t="s">
+      <c r="E22" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="F22" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="G22" s="40">
+      <c r="G22" s="34">
         <v>9515950</v>
       </c>
-      <c r="H22" s="41">
+      <c r="H22" s="35">
         <v>1</v>
       </c>
-      <c r="I22" s="63">
+      <c r="I22" s="55">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -2175,28 +2103,28 @@
     </row>
     <row r="23" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="38" t="s">
+        <v>173</v>
+      </c>
+      <c r="B23" s="31"/>
+      <c r="C23" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="D23" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="E23" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="F23" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" s="34" t="s">
         <v>162</v>
       </c>
-      <c r="D23" s="38" t="s">
-        <v>163</v>
-      </c>
-      <c r="E23" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="F23" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23" s="40" t="s">
-        <v>164</v>
-      </c>
-      <c r="H23" s="41">
+      <c r="H23" s="35">
         <v>0.4</v>
       </c>
-      <c r="I23" s="63">
+      <c r="I23" s="55">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
@@ -2204,175 +2132,196 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="47"/>
-      <c r="B24" s="14"/>
-      <c r="E24" s="48"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J24" s="10"/>
+    <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="B24" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="D24" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>214</v>
+      </c>
+      <c r="F24" s="32" t="s">
+        <v>215</v>
+      </c>
+      <c r="G24" s="37"/>
+      <c r="H24" s="38">
+        <v>29</v>
+      </c>
+      <c r="I24" s="55">
+        <f t="shared" ref="I24" si="1">J24*H24</f>
+        <v>29</v>
+      </c>
+      <c r="J24" s="10">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="B25" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="D25" s="38" t="s">
-        <v>217</v>
-      </c>
-      <c r="E25" s="42" t="s">
-        <v>218</v>
-      </c>
-      <c r="F25" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="G25" s="43"/>
-      <c r="H25" s="44">
-        <v>29</v>
-      </c>
-      <c r="I25" s="63">
-        <f t="shared" ref="I25" si="1">J25*H25</f>
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="F25" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="G25" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="H25" s="38">
+        <v>7</v>
+      </c>
+      <c r="I25" s="55">
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
       <c r="J25" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="D26" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="E26" s="42" t="s">
-        <v>89</v>
-      </c>
-      <c r="F26" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="G26" s="43" t="s">
-        <v>85</v>
-      </c>
-      <c r="H26" s="44">
-        <v>7</v>
-      </c>
-      <c r="I26" s="63">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <v>29</v>
+      </c>
+      <c r="B26" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="F26" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G26" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="H26" s="38">
+        <v>8.35</v>
+      </c>
+      <c r="I26" s="55">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
       </c>
       <c r="J26" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="E27" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="F27" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G27" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="H27" s="44">
-        <v>8.35</v>
-      </c>
-      <c r="I27" s="63">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
+      <c r="A27" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="E27" s="63" t="s">
+        <v>36</v>
+      </c>
+      <c r="F27" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G27" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="H27" s="38">
+        <v>0.7</v>
+      </c>
+      <c r="I27" s="55">
+        <f t="shared" ref="I27" si="2">J27*H27</f>
+        <v>0.7</v>
       </c>
       <c r="J27" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="38" t="s">
+      <c r="A28" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="B28" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="E28" s="71" t="s">
-        <v>36</v>
-      </c>
-      <c r="F28" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G28" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="H28" s="44">
-        <v>0.7</v>
-      </c>
-      <c r="I28" s="63">
-        <f t="shared" ref="I28" si="2">J28*H28</f>
-        <v>0.7</v>
+      <c r="D28" s="32" t="s">
+        <v>229</v>
+      </c>
+      <c r="E28" s="63" t="s">
+        <v>230</v>
+      </c>
+      <c r="F28" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28" s="39" t="s">
+        <v>231</v>
+      </c>
+      <c r="H28" s="38">
+        <v>1.4</v>
+      </c>
+      <c r="I28" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="J28" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="29" t="s">
-        <v>236</v>
-      </c>
-      <c r="B29" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D29" s="38" t="s">
-        <v>237</v>
-      </c>
-      <c r="E29" s="71" t="s">
-        <v>238</v>
-      </c>
-      <c r="F29" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G29" s="45" t="s">
-        <v>239</v>
-      </c>
-      <c r="H29" s="44">
-        <v>1.4</v>
-      </c>
-      <c r="I29" s="63">
-        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="60" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="E29" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="F29" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="G29" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="H29" s="53">
+        <v>0.35</v>
+      </c>
+      <c r="I29" s="54">
+        <f t="shared" ref="I29" si="3">J29*H29</f>
         <v>0</v>
       </c>
       <c r="J29" s="10">
@@ -2380,163 +2329,159 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="68" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="56" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="58" t="s">
-        <v>38</v>
-      </c>
-      <c r="D30" s="58" t="s">
-        <v>49</v>
-      </c>
-      <c r="E30" s="59" t="s">
-        <v>40</v>
-      </c>
-      <c r="F30" s="58" t="s">
-        <v>53</v>
-      </c>
-      <c r="G30" s="60" t="s">
-        <v>73</v>
-      </c>
-      <c r="H30" s="61">
+      <c r="A30" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="B30" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="D30" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="E30" s="36" t="s">
+        <v>188</v>
+      </c>
+      <c r="F30" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G30" s="37" t="s">
+        <v>187</v>
+      </c>
+      <c r="H30" s="38">
         <v>0.35</v>
       </c>
-      <c r="I30" s="62">
-        <f t="shared" ref="I30" si="3">J30*H30</f>
-        <v>0</v>
+      <c r="I30" s="55">
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="J30" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="B31" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="38" t="s">
-        <v>187</v>
-      </c>
-      <c r="D31" s="38" t="s">
-        <v>188</v>
-      </c>
-      <c r="E31" s="42" t="s">
+        <v>189</v>
+      </c>
+      <c r="B31" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="F31" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G31" s="43" t="s">
-        <v>189</v>
-      </c>
-      <c r="H31" s="44">
-        <v>0.35</v>
-      </c>
-      <c r="I31" s="63">
-        <f t="shared" si="0"/>
-        <v>0.35</v>
+      <c r="E31" s="36" t="s">
+        <v>191</v>
+      </c>
+      <c r="F31" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G31" s="39" t="s">
+        <v>192</v>
+      </c>
+      <c r="H31" s="38">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I31" s="55">
+        <f t="shared" si="0"/>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J31" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="B32" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="D32" s="38" t="s">
-        <v>192</v>
-      </c>
-      <c r="E32" s="42" t="s">
-        <v>193</v>
-      </c>
-      <c r="F32" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G32" s="45" t="s">
-        <v>194</v>
-      </c>
-      <c r="H32" s="44">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="I32" s="63">
-        <f t="shared" si="0"/>
-        <v>2.2000000000000002</v>
+        <v>128</v>
+      </c>
+      <c r="B32" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="E32" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="F32" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G32" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="H32" s="38">
+        <v>0.1</v>
+      </c>
+      <c r="I32" s="55">
+        <f t="shared" ref="I32:I33" si="4">J32*H32</f>
+        <v>0.4</v>
       </c>
       <c r="J32" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="B33" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="38" t="s">
+        <v>239</v>
+      </c>
+      <c r="B33" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D33" s="38" t="s">
-        <v>137</v>
-      </c>
-      <c r="E33" s="42" t="s">
-        <v>141</v>
-      </c>
-      <c r="F33" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G33" s="45" t="s">
-        <v>148</v>
-      </c>
-      <c r="H33" s="44">
-        <v>0.1</v>
-      </c>
-      <c r="I33" s="63">
-        <f t="shared" ref="I33" si="4">J33*H33</f>
+      <c r="D33" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="E33" s="63" t="s">
+        <v>233</v>
+      </c>
+      <c r="F33" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G33" s="39" t="s">
+        <v>235</v>
+      </c>
+      <c r="H33" s="38">
+        <v>0.2</v>
+      </c>
+      <c r="I33" s="55">
+        <f t="shared" si="4"/>
         <v>0.4</v>
       </c>
       <c r="J33" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="B34" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" s="32"/>
+      <c r="E34" s="63" t="s">
         <v>240</v>
       </c>
-      <c r="B34" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="D34" s="38" t="s">
-        <v>242</v>
-      </c>
-      <c r="E34" s="71" t="s">
-        <v>241</v>
-      </c>
-      <c r="F34" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G34" s="45" t="s">
-        <v>243</v>
-      </c>
-      <c r="H34" s="44">
+      <c r="F34" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G34" s="39"/>
+      <c r="H34" s="38">
         <v>0.2</v>
       </c>
-      <c r="I34" s="63">
+      <c r="I34" s="55">
         <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
@@ -2546,30 +2491,30 @@
     </row>
     <row r="35" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="B35" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="38" t="s">
+        <v>129</v>
+      </c>
+      <c r="B35" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D35" s="38" t="s">
-        <v>138</v>
-      </c>
-      <c r="E35" s="71" t="s">
-        <v>142</v>
-      </c>
-      <c r="F35" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G35" s="45" t="s">
-        <v>149</v>
-      </c>
-      <c r="H35" s="44">
+      <c r="D35" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="E35" s="63" t="s">
+        <v>140</v>
+      </c>
+      <c r="F35" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G35" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="H35" s="38">
         <v>0.1</v>
       </c>
-      <c r="I35" s="63">
+      <c r="I35" s="55">
         <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
@@ -2579,30 +2524,30 @@
     </row>
     <row r="36" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="B36" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="B36" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D36" s="38" t="s">
-        <v>109</v>
-      </c>
-      <c r="E36" s="42" t="s">
-        <v>143</v>
-      </c>
-      <c r="F36" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G36" s="45" t="s">
-        <v>150</v>
-      </c>
-      <c r="H36" s="44">
+      <c r="D36" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="E36" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="F36" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G36" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="H36" s="38">
         <v>0.1</v>
       </c>
-      <c r="I36" s="63">
+      <c r="I36" s="55">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
@@ -2612,30 +2557,30 @@
     </row>
     <row r="37" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="B37" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="B37" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D37" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="E37" s="42" t="s">
-        <v>144</v>
-      </c>
-      <c r="F37" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G37" s="45" t="s">
-        <v>151</v>
-      </c>
-      <c r="H37" s="44">
+      <c r="D37" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="E37" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="F37" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G37" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="H37" s="38">
         <v>0.1</v>
       </c>
-      <c r="I37" s="63">
+      <c r="I37" s="55">
         <f t="shared" ref="I37" si="5">J37*H37</f>
         <v>0.60000000000000009</v>
       </c>
@@ -2645,30 +2590,30 @@
     </row>
     <row r="38" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="B38" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="38" t="s">
+        <v>238</v>
+      </c>
+      <c r="B38" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D38" s="38" t="s">
-        <v>244</v>
-      </c>
-      <c r="E38" s="42" t="s">
-        <v>235</v>
-      </c>
-      <c r="F38" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G38" s="45" t="s">
-        <v>245</v>
-      </c>
-      <c r="H38" s="44">
+      <c r="D38" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="E38" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="F38" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G38" s="39" t="s">
+        <v>237</v>
+      </c>
+      <c r="H38" s="38">
         <v>0.1</v>
       </c>
-      <c r="I38" s="63">
+      <c r="I38" s="55">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
@@ -2678,30 +2623,30 @@
     </row>
     <row r="39" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="B39" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D39" s="38" t="s">
+      <c r="D39" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="E39" s="71" t="s">
-        <v>145</v>
-      </c>
-      <c r="F39" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G39" s="45" t="s">
-        <v>152</v>
-      </c>
-      <c r="H39" s="44">
+      <c r="E39" s="63" t="s">
+        <v>143</v>
+      </c>
+      <c r="F39" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G39" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="H39" s="38">
         <v>0.1</v>
       </c>
-      <c r="I39" s="63">
+      <c r="I39" s="55">
         <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
@@ -2711,30 +2656,30 @@
     </row>
     <row r="40" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="B40" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="38" t="s">
+        <v>133</v>
+      </c>
+      <c r="B40" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="38" t="s">
-        <v>139</v>
-      </c>
-      <c r="E40" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="F40" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G40" s="45" t="s">
-        <v>153</v>
-      </c>
-      <c r="H40" s="44">
+      <c r="D40" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="E40" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="F40" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G40" s="39" t="s">
+        <v>151</v>
+      </c>
+      <c r="H40" s="38">
         <v>0.1</v>
       </c>
-      <c r="I40" s="63">
+      <c r="I40" s="55">
         <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
@@ -2744,30 +2689,30 @@
     </row>
     <row r="41" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="B41" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="B41" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D41" s="38" t="s">
-        <v>140</v>
-      </c>
-      <c r="E41" s="42" t="s">
-        <v>147</v>
-      </c>
-      <c r="F41" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G41" s="45" t="s">
-        <v>154</v>
-      </c>
-      <c r="H41" s="44">
+      <c r="D41" s="32" t="s">
+        <v>138</v>
+      </c>
+      <c r="E41" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="F41" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G41" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="H41" s="38">
         <v>0.1</v>
       </c>
-      <c r="I41" s="63">
+      <c r="I41" s="55">
         <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
@@ -2776,197 +2721,197 @@
       </c>
     </row>
     <row r="42" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="67" t="s">
-        <v>86</v>
-      </c>
-      <c r="B42" s="56" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="58" t="s">
-        <v>112</v>
-      </c>
-      <c r="D42" s="58" t="s">
-        <v>113</v>
-      </c>
-      <c r="E42" s="59" t="s">
+      <c r="A42" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="B42" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="D42" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="E42" s="36" t="s">
         <v>196</v>
       </c>
-      <c r="F42" s="58" t="s">
-        <v>53</v>
-      </c>
-      <c r="G42" s="66" t="s">
+      <c r="F42" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G42" s="39" t="s">
         <v>197</v>
       </c>
-      <c r="H42" s="61">
+      <c r="H42" s="38">
+        <v>0.5</v>
+      </c>
+      <c r="I42" s="55">
+        <f t="shared" ref="I42" si="6">J42*H42</f>
+        <v>3</v>
+      </c>
+      <c r="J42" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="59" t="s">
+        <v>193</v>
+      </c>
+      <c r="B43" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="D43" s="50" t="s">
+        <v>198</v>
+      </c>
+      <c r="E43" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="F43" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="G43" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="H43" s="53">
+        <v>0.5</v>
+      </c>
+      <c r="I43" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="B44" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="32" t="s">
+        <v>172</v>
+      </c>
+      <c r="D44" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="E44" s="36" t="s">
+        <v>220</v>
+      </c>
+      <c r="F44" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G44" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="H44" s="38">
         <v>0.1</v>
       </c>
-      <c r="I42" s="62">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J42" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="B43" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="D43" s="38" t="s">
-        <v>199</v>
-      </c>
-      <c r="E43" s="42" t="s">
-        <v>200</v>
-      </c>
-      <c r="F43" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G43" s="45" t="s">
-        <v>201</v>
-      </c>
-      <c r="H43" s="44">
-        <v>0.5</v>
-      </c>
-      <c r="I43" s="63">
-        <f t="shared" ref="I43" si="6">J43*H43</f>
-        <v>3</v>
-      </c>
-      <c r="J43" s="10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="67" t="s">
-        <v>195</v>
-      </c>
-      <c r="B44" s="56" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="58" t="s">
-        <v>112</v>
-      </c>
-      <c r="D44" s="58" t="s">
-        <v>202</v>
-      </c>
-      <c r="E44" s="59" t="s">
-        <v>203</v>
-      </c>
-      <c r="F44" s="58" t="s">
-        <v>53</v>
-      </c>
-      <c r="G44" s="66" t="s">
-        <v>204</v>
-      </c>
-      <c r="H44" s="61">
-        <v>0.5</v>
-      </c>
-      <c r="I44" s="62">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="I44" s="55">
+        <f t="shared" ref="I44:I45" si="7">J44*H44</f>
+        <v>0.2</v>
       </c>
       <c r="J44" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="29" t="s">
-        <v>228</v>
-      </c>
-      <c r="B45" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="38" t="s">
-        <v>174</v>
-      </c>
-      <c r="D45" s="38" t="s">
-        <v>173</v>
-      </c>
-      <c r="E45" s="42" t="s">
-        <v>224</v>
-      </c>
-      <c r="F45" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G45" s="45" t="s">
+      <c r="A45" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="B45" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="H45" s="44">
+      <c r="D45" s="32" t="s">
+        <v>217</v>
+      </c>
+      <c r="E45" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="F45" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G45" s="39" t="s">
+        <v>218</v>
+      </c>
+      <c r="H45" s="38">
         <v>0.1</v>
       </c>
-      <c r="I45" s="63">
-        <f t="shared" ref="I45:I46" si="7">J45*H45</f>
-        <v>0.2</v>
-      </c>
-      <c r="J45" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="29" t="s">
-        <v>229</v>
-      </c>
-      <c r="B46" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="38" t="s">
-        <v>174</v>
-      </c>
-      <c r="D46" s="38" t="s">
-        <v>221</v>
-      </c>
-      <c r="E46" s="42" t="s">
-        <v>223</v>
-      </c>
-      <c r="F46" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G46" s="45" t="s">
-        <v>222</v>
-      </c>
-      <c r="H46" s="44">
-        <v>0.1</v>
-      </c>
-      <c r="I46" s="63">
+      <c r="I45" s="55">
         <f t="shared" si="7"/>
         <v>0.4</v>
       </c>
+      <c r="J45" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="D46" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="E46" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="F46" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G46" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="H46" s="38">
+        <v>0.3</v>
+      </c>
+      <c r="I46" s="55">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
       <c r="J46" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="67" t="s">
-        <v>230</v>
-      </c>
-      <c r="B47" s="56" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="58" t="s">
+      <c r="A47" s="59" t="s">
         <v>174</v>
       </c>
-      <c r="D47" s="58" t="s">
-        <v>225</v>
-      </c>
-      <c r="E47" s="59" t="s">
-        <v>226</v>
-      </c>
-      <c r="F47" s="58" t="s">
-        <v>53</v>
-      </c>
-      <c r="G47" s="66" t="s">
-        <v>227</v>
-      </c>
-      <c r="H47" s="61">
-        <v>0.3</v>
-      </c>
-      <c r="I47" s="62">
-        <f t="shared" si="0"/>
+      <c r="B47" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="50" t="s">
+        <v>179</v>
+      </c>
+      <c r="D47" s="50">
+        <v>161</v>
+      </c>
+      <c r="E47" s="51" t="s">
+        <v>175</v>
+      </c>
+      <c r="F47" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G47" s="56" t="s">
+        <v>176</v>
+      </c>
+      <c r="H47" s="53">
+        <v>1.2</v>
+      </c>
+      <c r="I47" s="54">
+        <f t="shared" ref="I47" si="8">J47*H47</f>
         <v>0</v>
       </c>
       <c r="J47" s="10">
@@ -2974,160 +2919,156 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="D48" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="E48" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="F48" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G48" s="45" t="s">
-        <v>74</v>
-      </c>
-      <c r="H48" s="44">
-        <v>0.3</v>
-      </c>
-      <c r="I48" s="63">
-        <f t="shared" si="0"/>
-        <v>0.3</v>
+      <c r="A48" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="B48" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="32" t="s">
+        <v>224</v>
+      </c>
+      <c r="D48" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="E48" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="F48" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G48" s="34" t="s">
+        <v>226</v>
+      </c>
+      <c r="H48" s="38">
+        <v>1.2</v>
+      </c>
+      <c r="I48" s="55">
+        <f t="shared" si="0"/>
+        <v>1.2</v>
       </c>
       <c r="J48" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="67" t="s">
-        <v>176</v>
-      </c>
-      <c r="B49" s="56" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="58" t="s">
-        <v>181</v>
-      </c>
-      <c r="D49" s="58">
-        <v>161</v>
-      </c>
-      <c r="E49" s="59" t="s">
-        <v>177</v>
-      </c>
-      <c r="F49" s="58" t="s">
+      <c r="A49" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="B49" s="31"/>
+      <c r="C49" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="D49" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E49" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="F49" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G49" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="H49" s="38">
         <v>1</v>
       </c>
-      <c r="G49" s="64" t="s">
-        <v>178</v>
-      </c>
-      <c r="H49" s="61">
-        <v>1.2</v>
-      </c>
-      <c r="I49" s="62">
-        <f t="shared" ref="I49" si="8">J49*H49</f>
+      <c r="I49" s="55">
+        <f t="shared" ref="I49:I51" si="9">J49*H49</f>
+        <v>2</v>
+      </c>
+      <c r="J49" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="59" t="s">
+        <v>207</v>
+      </c>
+      <c r="B50" s="48"/>
+      <c r="C50" s="50" t="s">
+        <v>201</v>
+      </c>
+      <c r="D50" s="50" t="s">
+        <v>210</v>
+      </c>
+      <c r="E50" s="51" t="s">
+        <v>208</v>
+      </c>
+      <c r="F50" s="50" t="s">
+        <v>209</v>
+      </c>
+      <c r="G50" s="56" t="s">
+        <v>211</v>
+      </c>
+      <c r="H50" s="53">
+        <v>1</v>
+      </c>
+      <c r="I50" s="54">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J49" s="10">
+      <c r="J50" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="29" t="s">
-        <v>231</v>
-      </c>
-      <c r="B50" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="38" t="s">
-        <v>232</v>
-      </c>
-      <c r="D50" s="38" t="s">
-        <v>233</v>
-      </c>
-      <c r="E50" s="42" t="s">
-        <v>177</v>
-      </c>
-      <c r="F50" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G50" s="40" t="s">
-        <v>234</v>
-      </c>
-      <c r="H50" s="44">
-        <v>1.2</v>
-      </c>
-      <c r="I50" s="63">
-        <f t="shared" si="0"/>
-        <v>1.2</v>
-      </c>
-      <c r="J50" s="10">
-        <v>1</v>
-      </c>
-    </row>
     <row r="51" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="29" t="s">
-        <v>114</v>
-      </c>
-      <c r="B51" s="37"/>
-      <c r="C51" s="38" t="s">
-        <v>126</v>
-      </c>
-      <c r="D51" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="E51" s="42" t="s">
-        <v>129</v>
-      </c>
-      <c r="F51" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G51" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="H51" s="44">
-        <v>1</v>
-      </c>
-      <c r="I51" s="63">
-        <f t="shared" ref="I51:I53" si="9">J51*H51</f>
-        <v>2</v>
+      <c r="A51" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="B51" s="31"/>
+      <c r="C51" s="32" t="s">
+        <v>201</v>
+      </c>
+      <c r="D51" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="E51" s="36" t="s">
+        <v>203</v>
+      </c>
+      <c r="F51" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G51" s="34" t="s">
+        <v>204</v>
+      </c>
+      <c r="H51" s="38">
+        <v>1.5</v>
+      </c>
+      <c r="I51" s="55">
+        <f t="shared" si="9"/>
+        <v>3</v>
       </c>
       <c r="J51" s="10">
         <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="67" t="s">
-        <v>211</v>
-      </c>
-      <c r="B52" s="56"/>
-      <c r="C52" s="58" t="s">
+      <c r="A52" s="59" t="s">
+        <v>207</v>
+      </c>
+      <c r="B52" s="48"/>
+      <c r="C52" s="50" t="s">
+        <v>179</v>
+      </c>
+      <c r="D52" s="50" t="s">
         <v>205</v>
       </c>
-      <c r="D52" s="58" t="s">
-        <v>214</v>
-      </c>
-      <c r="E52" s="59" t="s">
-        <v>212</v>
-      </c>
-      <c r="F52" s="58" t="s">
-        <v>213</v>
-      </c>
-      <c r="G52" s="64" t="s">
-        <v>215</v>
-      </c>
-      <c r="H52" s="61">
-        <v>1</v>
-      </c>
-      <c r="I52" s="62">
-        <f t="shared" si="9"/>
+      <c r="E52" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="F52" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="G52" s="56" t="s">
+        <v>178</v>
+      </c>
+      <c r="H52" s="53">
+        <v>1.8</v>
+      </c>
+      <c r="I52" s="54">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J52" s="10">
@@ -3135,221 +3076,225 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="B53" s="37"/>
-      <c r="C53" s="38" t="s">
-        <v>205</v>
-      </c>
-      <c r="D53" s="38" t="s">
-        <v>206</v>
-      </c>
-      <c r="E53" s="42" t="s">
-        <v>207</v>
-      </c>
-      <c r="F53" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G53" s="40" t="s">
-        <v>208</v>
-      </c>
-      <c r="H53" s="44">
-        <v>1.5</v>
-      </c>
-      <c r="I53" s="63">
-        <f t="shared" si="9"/>
-        <v>3</v>
+      <c r="A53" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="B53" s="31"/>
+      <c r="C53" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="32">
+        <v>2967989</v>
+      </c>
+      <c r="E53" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="F53" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G53" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="H53" s="38">
+        <v>38.6</v>
+      </c>
+      <c r="I53" s="55">
+        <f t="shared" si="0"/>
+        <v>38.6</v>
       </c>
       <c r="J53" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="B54" s="31"/>
+      <c r="C54" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D54" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="E54" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="F54" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G54" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="H54" s="38">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="I54" s="55">
+        <f>J54*H54</f>
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="J54" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B55" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" s="32">
+        <v>1755736</v>
+      </c>
+      <c r="E55" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="F55" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G55" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="H55" s="38">
+        <v>0.5</v>
+      </c>
+      <c r="I55" s="55">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="J55" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="67" t="s">
-        <v>211</v>
-      </c>
-      <c r="B54" s="56"/>
-      <c r="C54" s="58" t="s">
-        <v>181</v>
-      </c>
-      <c r="D54" s="58" t="s">
-        <v>209</v>
-      </c>
-      <c r="E54" s="59" t="s">
-        <v>179</v>
-      </c>
-      <c r="F54" s="58" t="s">
-        <v>53</v>
-      </c>
-      <c r="G54" s="64" t="s">
-        <v>180</v>
-      </c>
-      <c r="H54" s="61">
-        <v>1.8</v>
-      </c>
-      <c r="I54" s="62">
+    <row r="56" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B56" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" s="32">
+        <v>1754568</v>
+      </c>
+      <c r="E56" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="F56" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G56" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="H56" s="38">
+        <v>2.1</v>
+      </c>
+      <c r="I56" s="55">
+        <f t="shared" si="0"/>
+        <v>4.2</v>
+      </c>
+      <c r="J56" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="60" t="s">
+        <v>91</v>
+      </c>
+      <c r="B57" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" s="50">
+        <v>1755752</v>
+      </c>
+      <c r="E57" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="F57" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="G57" s="52" t="s">
+        <v>120</v>
+      </c>
+      <c r="H57" s="53">
+        <v>1.4</v>
+      </c>
+      <c r="I57" s="54">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J54" s="10">
+      <c r="J57" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="B55" s="37"/>
-      <c r="C55" s="46" t="s">
+    <row r="58" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="60" t="s">
+        <v>92</v>
+      </c>
+      <c r="B58" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="D55" s="38">
-        <v>2967989</v>
-      </c>
-      <c r="E55" s="42" t="s">
-        <v>124</v>
-      </c>
-      <c r="F55" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G55" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="H55" s="44">
-        <v>38.6</v>
-      </c>
-      <c r="I55" s="63">
-        <f t="shared" si="0"/>
-        <v>38.6</v>
-      </c>
-      <c r="J55" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="29" t="s">
-        <v>82</v>
-      </c>
-      <c r="B56" s="37"/>
-      <c r="C56" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D56" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="E56" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="F56" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G56" s="40" t="s">
-        <v>84</v>
-      </c>
-      <c r="H56" s="44">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="I56" s="63">
-        <f>J56*H56</f>
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="J56" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="B57" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="46" t="s">
+      <c r="D58" s="50">
+        <v>1754584</v>
+      </c>
+      <c r="E58" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="F58" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="G58" s="52" t="s">
+        <v>117</v>
+      </c>
+      <c r="H58" s="53">
+        <v>4.2</v>
+      </c>
+      <c r="I58" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="B59" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="D57" s="38">
-        <v>1755736</v>
-      </c>
-      <c r="E57" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="F57" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G57" s="43" t="s">
-        <v>120</v>
-      </c>
-      <c r="H57" s="44">
-        <v>0.5</v>
-      </c>
-      <c r="I57" s="63">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J57" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="B58" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C58" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="D58" s="38">
-        <v>1754568</v>
-      </c>
-      <c r="E58" s="71" t="s">
-        <v>97</v>
-      </c>
-      <c r="F58" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G58" s="43" t="s">
-        <v>121</v>
-      </c>
-      <c r="H58" s="44">
-        <v>2.1</v>
-      </c>
-      <c r="I58" s="63">
-        <f t="shared" si="0"/>
-        <v>4.2</v>
-      </c>
-      <c r="J58" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="68" t="s">
-        <v>92</v>
-      </c>
-      <c r="B59" s="56" t="s">
-        <v>6</v>
-      </c>
-      <c r="C59" s="57" t="s">
-        <v>7</v>
-      </c>
-      <c r="D59" s="58">
-        <v>1755752</v>
-      </c>
-      <c r="E59" s="59" t="s">
-        <v>96</v>
-      </c>
-      <c r="F59" s="58" t="s">
-        <v>53</v>
-      </c>
-      <c r="G59" s="60" t="s">
-        <v>122</v>
-      </c>
-      <c r="H59" s="61">
-        <v>1.4</v>
-      </c>
-      <c r="I59" s="62">
+      <c r="D59" s="50">
+        <v>1803426</v>
+      </c>
+      <c r="E59" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="F59" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="G59" s="52" t="s">
+        <v>54</v>
+      </c>
+      <c r="H59" s="38">
+        <v>0.6</v>
+      </c>
+      <c r="I59" s="55">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3358,31 +3303,31 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="68" t="s">
-        <v>93</v>
-      </c>
-      <c r="B60" s="56" t="s">
-        <v>6</v>
-      </c>
-      <c r="C60" s="57" t="s">
+      <c r="A60" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="B60" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="D60" s="58">
-        <v>1754584</v>
-      </c>
-      <c r="E60" s="59" t="s">
-        <v>95</v>
-      </c>
-      <c r="F60" s="58" t="s">
-        <v>53</v>
-      </c>
-      <c r="G60" s="60" t="s">
-        <v>119</v>
-      </c>
-      <c r="H60" s="61">
-        <v>4.2</v>
-      </c>
-      <c r="I60" s="62">
+      <c r="D60" s="50">
+        <v>1745894</v>
+      </c>
+      <c r="E60" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="F60" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="G60" s="52" t="s">
+        <v>57</v>
+      </c>
+      <c r="H60" s="38">
+        <v>1.7</v>
+      </c>
+      <c r="I60" s="55">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3391,165 +3336,165 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="68" t="s">
-        <v>52</v>
-      </c>
-      <c r="B61" s="56" t="s">
-        <v>6</v>
-      </c>
-      <c r="C61" s="57" t="s">
+      <c r="A61" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B61" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="D61" s="58">
-        <v>1803426</v>
-      </c>
-      <c r="E61" s="59" t="s">
-        <v>55</v>
-      </c>
-      <c r="F61" s="58" t="s">
-        <v>53</v>
-      </c>
-      <c r="G61" s="60" t="s">
-        <v>54</v>
-      </c>
-      <c r="H61" s="44">
-        <v>0.6</v>
-      </c>
-      <c r="I61" s="63">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="D61" s="32">
+        <v>1803439</v>
+      </c>
+      <c r="E61" s="36" t="s">
+        <v>180</v>
+      </c>
+      <c r="F61" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G61" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="H61" s="38">
+        <v>0.9</v>
+      </c>
+      <c r="I61" s="55">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
       </c>
       <c r="J61" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="68" t="s">
-        <v>56</v>
-      </c>
-      <c r="B62" s="56" t="s">
-        <v>6</v>
-      </c>
-      <c r="C62" s="57" t="s">
+      <c r="A62" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B62" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="D62" s="58">
-        <v>1745894</v>
-      </c>
-      <c r="E62" s="59" t="s">
-        <v>58</v>
-      </c>
-      <c r="F62" s="58" t="s">
-        <v>53</v>
-      </c>
-      <c r="G62" s="60" t="s">
-        <v>57</v>
-      </c>
-      <c r="H62" s="44">
-        <v>1.7</v>
-      </c>
-      <c r="I62" s="63">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="D62" s="32">
+        <v>1745904</v>
+      </c>
+      <c r="E62" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="F62" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G62" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="H62" s="38">
+        <v>2.5</v>
+      </c>
+      <c r="I62" s="55">
+        <f t="shared" si="0"/>
+        <v>2.5</v>
       </c>
       <c r="J62" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="B63" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C63" s="46" t="s">
+      <c r="B63" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="D63" s="38">
-        <v>1803439</v>
-      </c>
-      <c r="E63" s="42" t="s">
-        <v>182</v>
-      </c>
-      <c r="F63" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G63" s="43" t="s">
-        <v>185</v>
-      </c>
-      <c r="H63" s="44">
-        <v>0.9</v>
-      </c>
-      <c r="I63" s="63">
-        <f t="shared" si="0"/>
-        <v>0.9</v>
+      <c r="D63" s="32">
+        <v>1803442</v>
+      </c>
+      <c r="E63" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="F63" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G63" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="H63" s="38">
+        <v>1.2</v>
+      </c>
+      <c r="I63" s="55">
+        <f t="shared" si="0"/>
+        <v>3.5999999999999996</v>
       </c>
       <c r="J63" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B64" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C64" s="46" t="s">
+      <c r="B64" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="D64" s="38">
-        <v>1745904</v>
-      </c>
-      <c r="E64" s="42" t="s">
-        <v>183</v>
-      </c>
-      <c r="F64" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G64" s="43" t="s">
-        <v>184</v>
-      </c>
-      <c r="H64" s="44">
-        <v>2.5</v>
-      </c>
-      <c r="I64" s="63">
-        <f t="shared" si="0"/>
-        <v>2.5</v>
+      <c r="D64" s="32">
+        <v>1745917</v>
+      </c>
+      <c r="E64" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="F64" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G64" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="H64" s="38">
+        <v>3.4</v>
+      </c>
+      <c r="I64" s="55">
+        <f t="shared" si="0"/>
+        <v>10.199999999999999</v>
       </c>
       <c r="J64" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B65" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C65" s="46" t="s">
+        <v>65</v>
+      </c>
+      <c r="B65" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="D65" s="38">
-        <v>1803442</v>
-      </c>
-      <c r="E65" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="F65" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G65" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="H65" s="44">
-        <v>1.2</v>
-      </c>
-      <c r="I65" s="63">
-        <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+      <c r="D65" s="32">
+        <v>1803468</v>
+      </c>
+      <c r="E65" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="F65" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G65" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="H65" s="38">
+        <v>1.8</v>
+      </c>
+      <c r="I65" s="55">
+        <f t="shared" si="0"/>
+        <v>5.4</v>
       </c>
       <c r="J65" s="10">
         <v>3</v>
@@ -3557,142 +3502,64 @@
     </row>
     <row r="66" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="B66" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C66" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="B66" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="D66" s="38">
-        <v>1745917</v>
-      </c>
-      <c r="E66" s="42" t="s">
-        <v>63</v>
-      </c>
-      <c r="F66" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G66" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="H66" s="44">
-        <v>3.4</v>
-      </c>
-      <c r="I66" s="63">
-        <f t="shared" si="0"/>
-        <v>10.199999999999999</v>
+      <c r="D66" s="32">
+        <v>1748011</v>
+      </c>
+      <c r="E66" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="F66" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G66" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="H66" s="38">
+        <v>5.5</v>
+      </c>
+      <c r="I66" s="55">
+        <f t="shared" si="0"/>
+        <v>16.5</v>
       </c>
       <c r="J66" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="B67" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C67" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="D67" s="38">
-        <v>1803468</v>
-      </c>
-      <c r="E67" s="71" t="s">
-        <v>67</v>
-      </c>
-      <c r="F67" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G67" s="43" t="s">
-        <v>70</v>
-      </c>
-      <c r="H67" s="44">
-        <v>1.8</v>
-      </c>
-      <c r="I67" s="63">
-        <f t="shared" si="0"/>
-        <v>5.4</v>
-      </c>
-      <c r="J67" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="B68" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C68" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="D68" s="38">
-        <v>1748011</v>
-      </c>
-      <c r="E68" s="71" t="s">
-        <v>68</v>
-      </c>
-      <c r="F68" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G68" s="43" t="s">
-        <v>69</v>
-      </c>
-      <c r="H68" s="44">
-        <v>5.5</v>
-      </c>
-      <c r="I68" s="63">
-        <f t="shared" si="0"/>
-        <v>16.5</v>
-      </c>
-      <c r="J68" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="20"/>
-      <c r="B69" s="21"/>
-      <c r="C69" s="22"/>
-      <c r="D69" s="22"/>
-      <c r="E69" s="22"/>
-      <c r="F69" s="22"/>
-      <c r="G69" s="23"/>
-      <c r="H69" s="27"/>
-      <c r="I69" s="26"/>
-      <c r="J69" s="18"/>
-    </row>
-    <row r="70" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="33"/>
-      <c r="B70" s="34"/>
-      <c r="G70" s="35"/>
-      <c r="H70" s="31"/>
-      <c r="I70" s="31">
-        <f>SUM(I9:I68)</f>
-        <v>233.7999999999999</v>
-      </c>
-      <c r="J70" s="32" t="s">
+    <row r="67" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="27"/>
+      <c r="B67" s="28"/>
+      <c r="G67" s="29"/>
+      <c r="H67" s="25"/>
+      <c r="I67" s="25">
+        <f>SUM(I9:I66)</f>
+        <v>234.1999999999999</v>
+      </c>
+      <c r="J67" s="26" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="6"/>
-      <c r="B71" s="7"/>
-      <c r="C71" s="7"/>
-      <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="7"/>
-      <c r="G71" s="7"/>
-      <c r="H71" s="28"/>
-      <c r="I71" s="28"/>
-      <c r="J71" s="19"/>
+    <row r="68" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="6"/>
+      <c r="B68" s="7"/>
+      <c r="C68" s="7"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
+      <c r="G68" s="7"/>
+      <c r="H68" s="22"/>
+      <c r="I68" s="22"/>
+      <c r="J68" s="18"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:J71" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A5:J68" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="12">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A5:A6"/>
@@ -3708,7 +3575,7 @@
     <mergeCell ref="F5:F6"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
-  <conditionalFormatting sqref="J9:J68">
+  <conditionalFormatting sqref="J9:J66">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>

--- a/Unterlagen/Stueckliste_RevE_20260929.xlsx
+++ b/Unterlagen/Stueckliste_RevE_20260929.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_DIM\_GitHubRepository\ChickenGateSystem\Unterlagen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/01aac5d43cf7ca31/Dokumente/_NEPTUN__SyncNP3/GitHubRepositorys/ChickenGateSystem/Unterlagen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315754E0-5574-4A94-84BE-B6C92B608102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="13_ncr:1_{315754E0-5574-4A94-84BE-B6C92B608102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A5C070D-D346-4620-AE73-CB7E155E4D93}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stückliste" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_A100000">Stückliste!$A$9505</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Stückliste!$A$5:$J$68</definedName>
+    <definedName name="_A100000">Stückliste!$A$9507</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Stückliste!$A$5:$J$70</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="248">
   <si>
     <t>Art.-Nr.</t>
   </si>
@@ -330,33 +330,18 @@
     <t>DC/DC-Wandler, ITE, 1 Ausgang, 5 W, 5 V, 1 A, TSR 1 Series</t>
   </si>
   <si>
-    <t>Stromversorgung 5VDC (alternativ)</t>
-  </si>
-  <si>
     <t>DC/DC-Wandler, ITE, 1 Ausgang, 5 W, 5 V, 1 A</t>
   </si>
   <si>
     <t>LITTELFUSE</t>
   </si>
   <si>
-    <t xml:space="preserve">  Kondensator 100uF  /  12DC-Versorgung - Elko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Kondensator 22uF  /  5V-IC-Versorgung - Elko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Kondensator 100nF  /  5V-IC-Versorgung - Keramik</t>
-  </si>
-  <si>
     <t>Panasonic</t>
   </si>
   <si>
     <t>Elektrolytkondensator, 100 µF, 50 V, ±20%, Radial, 6000 Stunden/105°C</t>
   </si>
   <si>
-    <t>EEUFR1H101B</t>
-  </si>
-  <si>
     <t>MBB02070C2201FCT00</t>
   </si>
   <si>
@@ -588,9 +573,6 @@
     <t>651-1803439</t>
   </si>
   <si>
-    <t xml:space="preserve">  Quarz 16MHz - Alternative</t>
-  </si>
-  <si>
     <t>IQD</t>
   </si>
   <si>
@@ -720,9 +702,6 @@
     <t>Widerstand, 600mW, 4,7 kOhm, 1 %</t>
   </si>
   <si>
-    <t xml:space="preserve">  DIL-Sockel 28-polig - Alternative</t>
-  </si>
-  <si>
     <t>2485264-7</t>
   </si>
   <si>
@@ -732,9 +711,6 @@
     <t>571-2485264-7</t>
   </si>
   <si>
-    <t xml:space="preserve">  Widerstand 330 Ohm</t>
-  </si>
-  <si>
     <t>Widerstand, 600mW, 220 Ohm, 1 %</t>
   </si>
   <si>
@@ -756,7 +732,52 @@
     <t xml:space="preserve">  Widerstand 220 Ohm</t>
   </si>
   <si>
-    <t>Widerstand, 600mW, 330 Ohm, 1 %</t>
+    <t>MBB02070C4702FCT00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Widerstand 47 kOhm</t>
+  </si>
+  <si>
+    <t>Widerstand, 600mW, 47 kOhm, 1 %</t>
+  </si>
+  <si>
+    <t>594-MBB02070C4702FCT</t>
+  </si>
+  <si>
+    <t>EEU-FR1H101B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Kondensator 100uF  / 50V  /  12DC-Versorgung - Elko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Kondensator 470uF  / 25V   /  5V-IC-Versorgung - Elko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Kondensator 100nF  / 25V  /  5V-IC-Versorgung - Keramik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Kondensator 22uF  / 25V  /  5V-Nextion-Versorgung - Elko</t>
+  </si>
+  <si>
+    <t>EEU-FR1E471L</t>
+  </si>
+  <si>
+    <t>Elektrolytkondensator, 470 µF, 25 V, ±20%, Radial, 9000 Stunden/105°C</t>
+  </si>
+  <si>
+    <t>667-EEU-FR1E471L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Kondensator 470uF  / 50V  /  12DC-Versorgung - Elko</t>
+  </si>
+  <si>
+    <t>EEU-FR1H471</t>
+  </si>
+  <si>
+    <t>Elektrolytkondensator, 470 µF, 50 V, ±20%, Radial, 10000 Stunden/105°C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">667-EEU-FR1H471 </t>
   </si>
 </sst>
 </file>
@@ -1038,7 +1059,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1222,6 +1243,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1278,6 +1311,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1570,84 +1607,84 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:K68"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.1" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A2:K70"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="87.85546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.26953125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.453125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.81640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="87.81640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.26953125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="15" style="20" customWidth="1"/>
-    <col min="10" max="10" width="12.85546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="2.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.81640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="2.453125" style="1" customWidth="1"/>
     <col min="12" max="16384" width="0" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="64" t="s">
+    <row r="2" spans="1:11" ht="28.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="68" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-    </row>
-    <row r="5" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="65" t="s">
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+    </row>
+    <row r="5" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="65" t="s">
+      <c r="B5" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="65" t="s">
+      <c r="C5" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="65" t="s">
+      <c r="D5" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="65" t="s">
+      <c r="E5" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="65" t="s">
+      <c r="F5" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="70" t="s">
+      <c r="G5" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="H5" s="68" t="s">
+      <c r="H5" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="68" t="s">
+      <c r="I5" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="65" t="s">
+      <c r="J5" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="K5" s="67"/>
-    </row>
-    <row r="6" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="66"/>
-      <c r="B6" s="66"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
-    </row>
-    <row r="7" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K5" s="71"/>
+    </row>
+    <row r="6" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="70"/>
+      <c r="B6" s="70"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="75"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="71"/>
+    </row>
+    <row r="7" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -1660,7 +1697,7 @@
       <c r="J7" s="4"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="28.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>19</v>
       </c>
@@ -1668,7 +1705,7 @@
       <c r="E8" s="5"/>
       <c r="J8" s="10"/>
     </row>
-    <row r="9" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>20</v>
       </c>
@@ -1694,14 +1731,14 @@
         <v>50</v>
       </c>
       <c r="I9" s="55">
-        <f t="shared" ref="I9:I66" si="0">J9*H9</f>
+        <f t="shared" ref="I9:I68" si="0">J9*H9</f>
         <v>50</v>
       </c>
       <c r="J9" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>23</v>
       </c>
@@ -1734,7 +1771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="60" t="s">
         <v>11</v>
       </c>
@@ -1767,7 +1804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>15</v>
       </c>
@@ -1798,7 +1835,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="41"/>
       <c r="B13" s="14"/>
       <c r="E13" s="12"/>
@@ -1810,7 +1847,7 @@
       </c>
       <c r="J13" s="10"/>
     </row>
-    <row r="14" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="60" t="s">
         <v>75</v>
       </c>
@@ -1843,27 +1880,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="E15" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="B15" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="D15" s="32" t="s">
-        <v>155</v>
-      </c>
-      <c r="E15" s="36" t="s">
-        <v>99</v>
-      </c>
       <c r="F15" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="H15" s="35">
         <v>8.6</v>
@@ -1876,27 +1913,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E16" s="36" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F16" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G16" s="39" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="H16" s="38">
         <v>0.6</v>
@@ -1909,416 +1946,416 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>101</v>
+        <v>244</v>
       </c>
       <c r="B17" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>106</v>
-      </c>
-      <c r="E17" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="F17" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17" s="39" t="s">
-        <v>158</v>
-      </c>
-      <c r="H17" s="38">
-        <v>0.6</v>
-      </c>
-      <c r="I17" s="55">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>245</v>
+      </c>
+      <c r="E17" s="63" t="s">
+        <v>246</v>
+      </c>
+      <c r="F17" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" s="65" t="s">
+        <v>247</v>
+      </c>
+      <c r="H17" s="66">
+        <v>1.2</v>
+      </c>
+      <c r="I17" s="67">
+        <f t="shared" si="0"/>
+        <v>1.2</v>
       </c>
       <c r="J17" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="B18" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="D18" s="32" t="s">
-        <v>167</v>
-      </c>
-      <c r="E18" s="36" t="s">
-        <v>169</v>
-      </c>
-      <c r="F18" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18" s="39" t="s">
-        <v>168</v>
-      </c>
-      <c r="H18" s="38">
-        <v>0.2</v>
-      </c>
-      <c r="I18" s="55">
-        <f t="shared" si="0"/>
-        <v>0.2</v>
+    <row r="18" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="60" t="s">
+        <v>237</v>
+      </c>
+      <c r="B18" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" s="50" t="s">
+        <v>236</v>
+      </c>
+      <c r="E18" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="F18" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="58" t="s">
+        <v>153</v>
+      </c>
+      <c r="H18" s="53">
+        <v>0.6</v>
+      </c>
+      <c r="I18" s="54">
+        <f t="shared" ref="I18" si="1">J18*H18</f>
+        <v>0.6</v>
       </c>
       <c r="J18" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
-        <v>103</v>
+        <v>238</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>241</v>
+      </c>
+      <c r="E19" s="63" t="s">
+        <v>242</v>
+      </c>
+      <c r="F19" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="65" t="s">
+        <v>243</v>
+      </c>
+      <c r="H19" s="66">
+        <v>0.8</v>
+      </c>
+      <c r="I19" s="67">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="J19" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="60" t="s">
+        <v>240</v>
+      </c>
+      <c r="B20" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" s="50" t="s">
+        <v>162</v>
+      </c>
+      <c r="E20" s="51" t="s">
+        <v>164</v>
+      </c>
+      <c r="F20" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" s="58" t="s">
+        <v>163</v>
+      </c>
+      <c r="H20" s="53">
+        <v>0.2</v>
+      </c>
+      <c r="I20" s="54">
+        <f>J20*H20</f>
+        <v>0.2</v>
+      </c>
+      <c r="J20" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="32" t="s">
-        <v>165</v>
-      </c>
-      <c r="E19" s="63" t="s">
-        <v>164</v>
-      </c>
-      <c r="F19" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="H19" s="38">
+      <c r="D21" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="E21" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" s="39" t="s">
+        <v>161</v>
+      </c>
+      <c r="H21" s="38">
         <v>0.4</v>
       </c>
-      <c r="I19" s="55">
-        <f t="shared" si="0"/>
+      <c r="I21" s="55">
+        <f>J21*H21</f>
         <v>2.4000000000000004</v>
       </c>
-      <c r="J19" s="10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="17" t="s">
+      <c r="J21" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="17" t="s">
         <v>80</v>
-      </c>
-      <c r="B20" s="31"/>
-      <c r="C20" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="D20" s="32">
-        <v>55900000001</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="F20" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="H20" s="35">
-        <v>1</v>
-      </c>
-      <c r="I20" s="55">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="J20" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="B21" s="31"/>
-      <c r="C21" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="D21" s="32">
-        <v>37212000411</v>
-      </c>
-      <c r="E21" s="33" t="s">
-        <v>115</v>
-      </c>
-      <c r="F21" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="G21" s="34">
-        <v>2786441</v>
-      </c>
-      <c r="H21" s="35">
-        <v>1</v>
-      </c>
-      <c r="I21" s="55">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J21" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="17" t="s">
-        <v>81</v>
       </c>
       <c r="B22" s="31"/>
       <c r="C22" s="32" t="s">
         <v>79</v>
       </c>
       <c r="D22" s="32">
-        <v>37005000430</v>
-      </c>
-      <c r="E22" s="33" t="s">
-        <v>116</v>
+        <v>55900000001</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>108</v>
       </c>
       <c r="F22" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="G22" s="34">
-        <v>9515950</v>
+        <v>53</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>154</v>
       </c>
       <c r="H22" s="35">
         <v>1</v>
       </c>
       <c r="I22" s="55">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
-        <v>173</v>
+        <v>109</v>
       </c>
       <c r="B23" s="31"/>
       <c r="C23" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>161</v>
+        <v>79</v>
+      </c>
+      <c r="D23" s="32">
+        <v>37212000411</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>163</v>
+        <v>110</v>
       </c>
       <c r="F23" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23" s="34" t="s">
-        <v>162</v>
+        <v>34</v>
+      </c>
+      <c r="G23" s="34">
+        <v>2786441</v>
       </c>
       <c r="H23" s="35">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="I23" s="55">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J23" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="B24" s="31" t="s">
-        <v>6</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="B24" s="31"/>
       <c r="C24" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>213</v>
-      </c>
-      <c r="E24" s="36" t="s">
-        <v>214</v>
+        <v>79</v>
+      </c>
+      <c r="D24" s="32">
+        <v>37005000430</v>
+      </c>
+      <c r="E24" s="33" t="s">
+        <v>111</v>
       </c>
       <c r="F24" s="32" t="s">
-        <v>215</v>
-      </c>
-      <c r="G24" s="37"/>
-      <c r="H24" s="38">
-        <v>29</v>
+        <v>34</v>
+      </c>
+      <c r="G24" s="34">
+        <v>9515950</v>
+      </c>
+      <c r="H24" s="35">
+        <v>1</v>
       </c>
       <c r="I24" s="55">
-        <f t="shared" ref="I24" si="1">J24*H24</f>
-        <v>29</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="J24" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" s="31" t="s">
-        <v>6</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="B25" s="31"/>
       <c r="C25" s="32" t="s">
-        <v>31</v>
+        <v>155</v>
       </c>
       <c r="D25" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="E25" s="36" t="s">
-        <v>88</v>
+        <v>156</v>
+      </c>
+      <c r="E25" s="33" t="s">
+        <v>158</v>
       </c>
       <c r="F25" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G25" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="H25" s="38">
-        <v>7</v>
+        <v>53</v>
+      </c>
+      <c r="G25" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="H25" s="35">
+        <v>0.4</v>
       </c>
       <c r="I25" s="55">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>0.8</v>
       </c>
       <c r="J25" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="B26" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>206</v>
+      </c>
+      <c r="D26" s="32" t="s">
+        <v>207</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>208</v>
+      </c>
+      <c r="F26" s="32" t="s">
+        <v>209</v>
+      </c>
+      <c r="G26" s="37"/>
+      <c r="H26" s="38">
         <v>29</v>
       </c>
-      <c r="B26" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="E26" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="F26" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G26" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="H26" s="38">
-        <v>8.35</v>
-      </c>
       <c r="I26" s="55">
-        <f t="shared" si="0"/>
-        <v>8.35</v>
+        <f t="shared" ref="I26" si="2">J26*H26</f>
+        <v>29</v>
       </c>
       <c r="J26" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="23" t="s">
-        <v>30</v>
+    <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="17" t="s">
+        <v>28</v>
       </c>
       <c r="B27" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="32" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D27" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="E27" s="63" t="s">
-        <v>36</v>
+        <v>46</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>88</v>
       </c>
       <c r="F27" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G27" s="39" t="s">
-        <v>72</v>
+        <v>1</v>
+      </c>
+      <c r="G27" s="37" t="s">
+        <v>85</v>
       </c>
       <c r="H27" s="38">
-        <v>0.7</v>
+        <v>7</v>
       </c>
       <c r="I27" s="55">
-        <f t="shared" ref="I27" si="2">J27*H27</f>
-        <v>0.7</v>
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
       <c r="J27" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="23" t="s">
-        <v>228</v>
+    <row r="28" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="17" t="s">
+        <v>29</v>
       </c>
       <c r="B28" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="F28" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="H28" s="38">
+        <v>8.35</v>
+      </c>
+      <c r="I28" s="55">
+        <f t="shared" si="0"/>
+        <v>8.35</v>
+      </c>
+      <c r="J28" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="59" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="32" t="s">
-        <v>229</v>
-      </c>
-      <c r="E28" s="63" t="s">
-        <v>230</v>
-      </c>
-      <c r="F28" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G28" s="39" t="s">
-        <v>231</v>
-      </c>
-      <c r="H28" s="38">
-        <v>1.4</v>
-      </c>
-      <c r="I28" s="55">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J28" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="60" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="50" t="s">
-        <v>38</v>
-      </c>
       <c r="D29" s="50" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F29" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="G29" s="52" t="s">
-        <v>73</v>
+      <c r="G29" s="58" t="s">
+        <v>72</v>
       </c>
       <c r="H29" s="53">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="I29" s="54">
         <f t="shared" ref="I29" si="3">J29*H29</f>
@@ -2328,141 +2365,141 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="17" t="s">
-        <v>184</v>
+    <row r="30" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="23" t="s">
+        <v>30</v>
       </c>
       <c r="B30" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="32" t="s">
-        <v>185</v>
+        <v>33</v>
       </c>
       <c r="D30" s="32" t="s">
-        <v>186</v>
-      </c>
-      <c r="E30" s="36" t="s">
-        <v>188</v>
-      </c>
-      <c r="F30" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G30" s="37" t="s">
-        <v>187</v>
-      </c>
-      <c r="H30" s="38">
-        <v>0.35</v>
-      </c>
-      <c r="I30" s="55">
-        <f t="shared" si="0"/>
-        <v>0.35</v>
+        <v>222</v>
+      </c>
+      <c r="E30" s="63" t="s">
+        <v>223</v>
+      </c>
+      <c r="F30" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="G30" s="65" t="s">
+        <v>224</v>
+      </c>
+      <c r="H30" s="66">
+        <v>1.4</v>
+      </c>
+      <c r="I30" s="67">
+        <f t="shared" si="0"/>
+        <v>1.4</v>
       </c>
       <c r="J30" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="B31" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="32" t="s">
+    <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="60" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="E31" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="F31" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="G31" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="H31" s="53">
+        <v>0.35</v>
+      </c>
+      <c r="I31" s="54">
+        <f t="shared" ref="I31" si="4">J31*H31</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="D32" s="32" t="s">
+        <v>180</v>
+      </c>
+      <c r="E32" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="F32" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G32" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="H32" s="38">
+        <v>0.35</v>
+      </c>
+      <c r="I32" s="55">
+        <f t="shared" si="0"/>
+        <v>0.35</v>
+      </c>
+      <c r="J32" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="B33" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="D31" s="32" t="s">
-        <v>190</v>
-      </c>
-      <c r="E31" s="36" t="s">
-        <v>191</v>
-      </c>
-      <c r="F31" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G31" s="39" t="s">
-        <v>192</v>
-      </c>
-      <c r="H31" s="38">
+      <c r="D33" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="E33" s="36" t="s">
+        <v>185</v>
+      </c>
+      <c r="F33" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G33" s="39" t="s">
+        <v>186</v>
+      </c>
+      <c r="H33" s="38">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I31" s="55">
-        <f t="shared" si="0"/>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="J31" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="B32" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="D32" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="E32" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="F32" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G32" s="39" t="s">
-        <v>146</v>
-      </c>
-      <c r="H32" s="38">
-        <v>0.1</v>
-      </c>
-      <c r="I32" s="55">
-        <f t="shared" ref="I32:I33" si="4">J32*H32</f>
-        <v>0.4</v>
-      </c>
-      <c r="J32" s="10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="17" t="s">
-        <v>239</v>
-      </c>
-      <c r="B33" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="D33" s="32" t="s">
-        <v>234</v>
-      </c>
-      <c r="E33" s="63" t="s">
-        <v>233</v>
-      </c>
-      <c r="F33" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G33" s="39" t="s">
-        <v>235</v>
-      </c>
-      <c r="H33" s="38">
-        <v>0.2</v>
-      </c>
       <c r="I33" s="55">
-        <f t="shared" si="4"/>
-        <v>0.4</v>
+        <f t="shared" si="0"/>
+        <v>3.3000000000000003</v>
       </c>
       <c r="J33" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
-        <v>232</v>
+        <v>123</v>
       </c>
       <c r="B34" s="31" t="s">
         <v>6</v>
@@ -2470,28 +2507,32 @@
       <c r="C34" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D34" s="32"/>
-      <c r="E34" s="63" t="s">
-        <v>240</v>
+      <c r="D34" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="E34" s="36" t="s">
+        <v>134</v>
       </c>
       <c r="F34" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="G34" s="39"/>
+      <c r="G34" s="39" t="s">
+        <v>141</v>
+      </c>
       <c r="H34" s="38">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I34" s="55">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I34:I35" si="5">J34*H34</f>
         <v>0.4</v>
       </c>
       <c r="J34" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
-        <v>129</v>
+        <v>231</v>
       </c>
       <c r="B35" s="31" t="s">
         <v>6</v>
@@ -2500,31 +2541,31 @@
         <v>42</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>136</v>
+        <v>226</v>
       </c>
       <c r="E35" s="63" t="s">
-        <v>140</v>
+        <v>225</v>
       </c>
       <c r="F35" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G35" s="39" t="s">
-        <v>147</v>
+        <v>227</v>
       </c>
       <c r="H35" s="38">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I35" s="55">
-        <f t="shared" si="0"/>
-        <v>0.2</v>
+        <f t="shared" si="5"/>
+        <v>0.4</v>
       </c>
       <c r="J35" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="17" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B36" s="31" t="s">
         <v>6</v>
@@ -2533,31 +2574,31 @@
         <v>42</v>
       </c>
       <c r="D36" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="E36" s="36" t="s">
-        <v>141</v>
+        <v>131</v>
+      </c>
+      <c r="E36" s="63" t="s">
+        <v>135</v>
       </c>
       <c r="F36" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G36" s="39" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="H36" s="38">
         <v>0.1</v>
       </c>
       <c r="I36" s="55">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J36" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="17" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B37" s="31" t="s">
         <v>6</v>
@@ -2566,31 +2607,31 @@
         <v>42</v>
       </c>
       <c r="D37" s="32" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E37" s="36" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="F37" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G37" s="39" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="H37" s="38">
         <v>0.1</v>
       </c>
       <c r="I37" s="55">
-        <f t="shared" ref="I37" si="5">J37*H37</f>
-        <v>0.60000000000000009</v>
+        <f t="shared" si="0"/>
+        <v>0.1</v>
       </c>
       <c r="J37" s="10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="17" t="s">
-        <v>238</v>
+        <v>126</v>
       </c>
       <c r="B38" s="31" t="s">
         <v>6</v>
@@ -2599,31 +2640,31 @@
         <v>42</v>
       </c>
       <c r="D38" s="32" t="s">
-        <v>236</v>
+        <v>102</v>
       </c>
       <c r="E38" s="36" t="s">
-        <v>227</v>
+        <v>137</v>
       </c>
       <c r="F38" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G38" s="39" t="s">
-        <v>237</v>
+        <v>144</v>
       </c>
       <c r="H38" s="38">
         <v>0.1</v>
       </c>
       <c r="I38" s="55">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
+        <f t="shared" ref="I38" si="6">J38*H38</f>
+        <v>0.60000000000000009</v>
       </c>
       <c r="J38" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="17" t="s">
-        <v>132</v>
+        <v>230</v>
       </c>
       <c r="B39" s="31" t="s">
         <v>6</v>
@@ -2632,31 +2673,31 @@
         <v>42</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="E39" s="63" t="s">
-        <v>143</v>
+        <v>228</v>
+      </c>
+      <c r="E39" s="36" t="s">
+        <v>221</v>
       </c>
       <c r="F39" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G39" s="39" t="s">
-        <v>150</v>
+        <v>229</v>
       </c>
       <c r="H39" s="38">
         <v>0.1</v>
       </c>
       <c r="I39" s="55">
         <f t="shared" si="0"/>
-        <v>1.1000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="J39" s="10">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="17" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B40" s="31" t="s">
         <v>6</v>
@@ -2665,31 +2706,31 @@
         <v>42</v>
       </c>
       <c r="D40" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="E40" s="36" t="s">
-        <v>144</v>
+        <v>50</v>
+      </c>
+      <c r="E40" s="63" t="s">
+        <v>138</v>
       </c>
       <c r="F40" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G40" s="39" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="H40" s="38">
         <v>0.1</v>
       </c>
       <c r="I40" s="55">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J40" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="17" t="s">
-        <v>134</v>
+        <v>233</v>
       </c>
       <c r="B41" s="31" t="s">
         <v>6</v>
@@ -2698,580 +2739,580 @@
         <v>42</v>
       </c>
       <c r="D41" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="E41" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="F41" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G41" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="H41" s="38">
+        <v>232</v>
+      </c>
+      <c r="E41" s="63" t="s">
+        <v>234</v>
+      </c>
+      <c r="F41" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="G41" s="65" t="s">
+        <v>235</v>
+      </c>
+      <c r="H41" s="66">
         <v>0.1</v>
       </c>
-      <c r="I41" s="55">
+      <c r="I41" s="67">
+        <f t="shared" ref="I41" si="7">J41*H41</f>
+        <v>0.1</v>
+      </c>
+      <c r="J41" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="B42" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="D42" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="E42" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="F42" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G42" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="H42" s="38">
+        <v>0.1</v>
+      </c>
+      <c r="I42" s="55">
         <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
-      <c r="J41" s="10">
+      <c r="J42" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="23" t="s">
+    <row r="43" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="B43" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="D43" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="E43" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="F43" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G43" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="H43" s="38">
+        <v>0.1</v>
+      </c>
+      <c r="I43" s="55">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="J43" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="B44" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="D44" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="F44" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G44" s="39" t="s">
+        <v>191</v>
+      </c>
+      <c r="H44" s="38">
+        <v>0.5</v>
+      </c>
+      <c r="I44" s="55">
+        <f t="shared" ref="I44" si="8">J44*H44</f>
+        <v>3</v>
+      </c>
+      <c r="J44" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="59" t="s">
+        <v>187</v>
+      </c>
+      <c r="B45" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="D45" s="50" t="s">
+        <v>192</v>
+      </c>
+      <c r="E45" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="F45" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="G45" s="58" t="s">
         <v>194</v>
       </c>
-      <c r="B42" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="32" t="s">
-        <v>111</v>
-      </c>
-      <c r="D42" s="32" t="s">
-        <v>195</v>
-      </c>
-      <c r="E42" s="36" t="s">
-        <v>196</v>
-      </c>
-      <c r="F42" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G42" s="39" t="s">
-        <v>197</v>
-      </c>
-      <c r="H42" s="38">
+      <c r="H45" s="53">
         <v>0.5</v>
       </c>
-      <c r="I42" s="55">
-        <f t="shared" ref="I42" si="6">J42*H42</f>
-        <v>3</v>
-      </c>
-      <c r="J42" s="10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="59" t="s">
-        <v>193</v>
-      </c>
-      <c r="B43" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="50" t="s">
-        <v>111</v>
-      </c>
-      <c r="D43" s="50" t="s">
-        <v>198</v>
-      </c>
-      <c r="E43" s="51" t="s">
-        <v>199</v>
-      </c>
-      <c r="F43" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="G43" s="58" t="s">
-        <v>200</v>
-      </c>
-      <c r="H43" s="53">
-        <v>0.5</v>
-      </c>
-      <c r="I43" s="54">
+      <c r="I45" s="54">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J43" s="10">
+      <c r="J45" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="B44" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="D44" s="32" t="s">
-        <v>171</v>
-      </c>
-      <c r="E44" s="36" t="s">
-        <v>220</v>
-      </c>
-      <c r="F44" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G44" s="39" t="s">
-        <v>170</v>
-      </c>
-      <c r="H44" s="38">
+    <row r="46" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="B46" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="D46" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="E46" s="36" t="s">
+        <v>214</v>
+      </c>
+      <c r="F46" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G46" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="H46" s="38">
         <v>0.1</v>
       </c>
-      <c r="I44" s="55">
-        <f t="shared" ref="I44:I45" si="7">J44*H44</f>
+      <c r="I46" s="55">
+        <f t="shared" ref="I46:I47" si="9">J46*H46</f>
         <v>0.2</v>
       </c>
-      <c r="J44" s="10">
+      <c r="J46" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="B45" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="D45" s="32" t="s">
-        <v>217</v>
-      </c>
-      <c r="E45" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="F45" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G45" s="39" t="s">
-        <v>218</v>
-      </c>
-      <c r="H45" s="38">
+    <row r="47" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="B47" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="D47" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="E47" s="36" t="s">
+        <v>213</v>
+      </c>
+      <c r="F47" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G47" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="H47" s="38">
         <v>0.1</v>
       </c>
-      <c r="I45" s="55">
-        <f t="shared" si="7"/>
+      <c r="I47" s="55">
+        <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
-      <c r="J45" s="10">
+      <c r="J47" s="10">
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="23" t="s">
+    <row r="48" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="32" t="s">
+      <c r="B48" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="D46" s="32" t="s">
+      <c r="D48" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E46" s="36" t="s">
+      <c r="E48" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="F46" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G46" s="39" t="s">
+      <c r="F48" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G48" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="H46" s="38">
+      <c r="H48" s="38">
         <v>0.3</v>
       </c>
-      <c r="I46" s="55">
+      <c r="I48" s="55">
         <f t="shared" si="0"/>
         <v>0.3</v>
-      </c>
-      <c r="J46" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="59" t="s">
-        <v>174</v>
-      </c>
-      <c r="B47" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="50" t="s">
-        <v>179</v>
-      </c>
-      <c r="D47" s="50">
-        <v>161</v>
-      </c>
-      <c r="E47" s="51" t="s">
-        <v>175</v>
-      </c>
-      <c r="F47" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="G47" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="H47" s="53">
-        <v>1.2</v>
-      </c>
-      <c r="I47" s="54">
-        <f t="shared" ref="I47" si="8">J47*H47</f>
-        <v>0</v>
-      </c>
-      <c r="J47" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="B48" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="32" t="s">
-        <v>224</v>
-      </c>
-      <c r="D48" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="E48" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="F48" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G48" s="34" t="s">
-        <v>226</v>
-      </c>
-      <c r="H48" s="38">
-        <v>1.2</v>
-      </c>
-      <c r="I48" s="55">
-        <f t="shared" si="0"/>
-        <v>1.2</v>
       </c>
       <c r="J48" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="B49" s="31"/>
-      <c r="C49" s="32" t="s">
-        <v>124</v>
-      </c>
-      <c r="D49" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E49" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="F49" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G49" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="H49" s="38">
+    <row r="49" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="59" t="s">
+        <v>169</v>
+      </c>
+      <c r="B49" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="50" t="s">
+        <v>174</v>
+      </c>
+      <c r="D49" s="50">
+        <v>161</v>
+      </c>
+      <c r="E49" s="51" t="s">
+        <v>170</v>
+      </c>
+      <c r="F49" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="I49" s="55">
-        <f t="shared" ref="I49:I51" si="9">J49*H49</f>
-        <v>2</v>
+      <c r="G49" s="56" t="s">
+        <v>171</v>
+      </c>
+      <c r="H49" s="53">
+        <v>1.2</v>
+      </c>
+      <c r="I49" s="54">
+        <f t="shared" ref="I49" si="10">J49*H49</f>
+        <v>0</v>
       </c>
       <c r="J49" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="59" t="s">
-        <v>207</v>
-      </c>
-      <c r="B50" s="48"/>
-      <c r="C50" s="50" t="s">
-        <v>201</v>
-      </c>
-      <c r="D50" s="50" t="s">
-        <v>210</v>
-      </c>
-      <c r="E50" s="51" t="s">
-        <v>208</v>
-      </c>
-      <c r="F50" s="50" t="s">
-        <v>209</v>
-      </c>
-      <c r="G50" s="56" t="s">
-        <v>211</v>
-      </c>
-      <c r="H50" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="23" t="s">
+        <v>217</v>
+      </c>
+      <c r="B50" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="32" t="s">
+        <v>218</v>
+      </c>
+      <c r="D50" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="E50" s="36" t="s">
+        <v>170</v>
+      </c>
+      <c r="F50" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G50" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="H50" s="38">
+        <v>1.2</v>
+      </c>
+      <c r="I50" s="55">
+        <f t="shared" si="0"/>
+        <v>1.2</v>
+      </c>
+      <c r="J50" s="10">
         <v>1</v>
       </c>
-      <c r="I50" s="54">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="J50" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="23" t="s">
-        <v>206</v>
+        <v>107</v>
       </c>
       <c r="B51" s="31"/>
       <c r="C51" s="32" t="s">
-        <v>201</v>
+        <v>119</v>
       </c>
       <c r="D51" s="32" t="s">
-        <v>202</v>
+        <v>120</v>
       </c>
       <c r="E51" s="36" t="s">
-        <v>203</v>
+        <v>122</v>
       </c>
       <c r="F51" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G51" s="34" t="s">
-        <v>204</v>
+        <v>121</v>
       </c>
       <c r="H51" s="38">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I51" s="55">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="I51:I53" si="11">J51*H51</f>
+        <v>2</v>
       </c>
       <c r="J51" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="59" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B52" s="48"/>
       <c r="C52" s="50" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="D52" s="50" t="s">
+        <v>204</v>
+      </c>
+      <c r="E52" s="51" t="s">
+        <v>202</v>
+      </c>
+      <c r="F52" s="50" t="s">
+        <v>203</v>
+      </c>
+      <c r="G52" s="56" t="s">
         <v>205</v>
       </c>
-      <c r="E52" s="51" t="s">
-        <v>177</v>
-      </c>
-      <c r="F52" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="G52" s="56" t="s">
-        <v>178</v>
-      </c>
       <c r="H52" s="53">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="I52" s="54">
-        <f t="shared" si="0"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J52" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="23" t="s">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="B53" s="31"/>
-      <c r="C53" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D53" s="32">
-        <v>2967989</v>
+      <c r="C53" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="D53" s="32" t="s">
+        <v>196</v>
       </c>
       <c r="E53" s="36" t="s">
-        <v>122</v>
+        <v>197</v>
       </c>
       <c r="F53" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G53" s="34" t="s">
-        <v>123</v>
+        <v>198</v>
       </c>
       <c r="H53" s="38">
-        <v>38.6</v>
+        <v>1.5</v>
       </c>
       <c r="I53" s="55">
-        <f t="shared" si="0"/>
-        <v>38.6</v>
+        <f t="shared" si="11"/>
+        <v>3</v>
       </c>
       <c r="J53" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="B54" s="31"/>
-      <c r="C54" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="D54" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="E54" s="36" t="s">
-        <v>86</v>
-      </c>
-      <c r="F54" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G54" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="H54" s="38">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="I54" s="55">
-        <f>J54*H54</f>
-        <v>8.6999999999999993</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="59" t="s">
+        <v>201</v>
+      </c>
+      <c r="B54" s="48"/>
+      <c r="C54" s="50" t="s">
+        <v>174</v>
+      </c>
+      <c r="D54" s="50" t="s">
+        <v>199</v>
+      </c>
+      <c r="E54" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="F54" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="G54" s="56" t="s">
+        <v>173</v>
+      </c>
+      <c r="H54" s="53">
+        <v>1.8</v>
+      </c>
+      <c r="I54" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="J54" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="B55" s="31" t="s">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="B55" s="31"/>
       <c r="C55" s="40" t="s">
         <v>7</v>
       </c>
       <c r="D55" s="32">
+        <v>2967989</v>
+      </c>
+      <c r="E55" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="F55" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G55" s="34" t="s">
+        <v>118</v>
+      </c>
+      <c r="H55" s="38">
+        <v>38.6</v>
+      </c>
+      <c r="I55" s="55">
+        <f t="shared" si="0"/>
+        <v>38.6</v>
+      </c>
+      <c r="J55" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="B56" s="31"/>
+      <c r="C56" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D56" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="E56" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="F56" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G56" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="H56" s="38">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="I56" s="55">
+        <f>J56*H56</f>
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="J56" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B57" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" s="32">
         <v>1755736</v>
       </c>
-      <c r="E55" s="36" t="s">
+      <c r="E57" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="F55" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G55" s="37" t="s">
-        <v>118</v>
-      </c>
-      <c r="H55" s="38">
+      <c r="F57" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G57" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="H57" s="38">
         <v>0.5</v>
       </c>
-      <c r="I55" s="55">
+      <c r="I57" s="55">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J55" s="10">
+      <c r="J57" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="17" t="s">
+    <row r="58" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B56" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C56" s="40" t="s">
+      <c r="B58" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="D56" s="32">
+      <c r="D58" s="32">
         <v>1754568</v>
       </c>
-      <c r="E56" s="63" t="s">
+      <c r="E58" s="63" t="s">
         <v>96</v>
       </c>
-      <c r="F56" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G56" s="37" t="s">
-        <v>119</v>
-      </c>
-      <c r="H56" s="38">
+      <c r="F58" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G58" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="H58" s="38">
         <v>2.1</v>
       </c>
-      <c r="I56" s="55">
+      <c r="I58" s="55">
         <f t="shared" si="0"/>
         <v>4.2</v>
       </c>
-      <c r="J56" s="10">
+      <c r="J58" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="60" t="s">
+    <row r="59" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="60" t="s">
         <v>91</v>
-      </c>
-      <c r="B57" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="49" t="s">
-        <v>7</v>
-      </c>
-      <c r="D57" s="50">
-        <v>1755752</v>
-      </c>
-      <c r="E57" s="51" t="s">
-        <v>95</v>
-      </c>
-      <c r="F57" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="G57" s="52" t="s">
-        <v>120</v>
-      </c>
-      <c r="H57" s="53">
-        <v>1.4</v>
-      </c>
-      <c r="I57" s="54">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J57" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="60" t="s">
-        <v>92</v>
-      </c>
-      <c r="B58" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="C58" s="49" t="s">
-        <v>7</v>
-      </c>
-      <c r="D58" s="50">
-        <v>1754584</v>
-      </c>
-      <c r="E58" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="F58" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="G58" s="52" t="s">
-        <v>117</v>
-      </c>
-      <c r="H58" s="53">
-        <v>4.2</v>
-      </c>
-      <c r="I58" s="54">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J58" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="60" t="s">
-        <v>52</v>
       </c>
       <c r="B59" s="48" t="s">
         <v>6</v>
@@ -3280,21 +3321,21 @@
         <v>7</v>
       </c>
       <c r="D59" s="50">
-        <v>1803426</v>
+        <v>1755752</v>
       </c>
       <c r="E59" s="51" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="F59" s="50" t="s">
         <v>53</v>
       </c>
       <c r="G59" s="52" t="s">
-        <v>54</v>
-      </c>
-      <c r="H59" s="38">
-        <v>0.6</v>
-      </c>
-      <c r="I59" s="55">
+        <v>115</v>
+      </c>
+      <c r="H59" s="53">
+        <v>1.4</v>
+      </c>
+      <c r="I59" s="54">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3302,9 +3343,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="60" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="B60" s="48" t="s">
         <v>6</v>
@@ -3313,21 +3354,21 @@
         <v>7</v>
       </c>
       <c r="D60" s="50">
-        <v>1745894</v>
+        <v>1754584</v>
       </c>
       <c r="E60" s="51" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="F60" s="50" t="s">
         <v>53</v>
       </c>
       <c r="G60" s="52" t="s">
-        <v>57</v>
-      </c>
-      <c r="H60" s="38">
-        <v>1.7</v>
-      </c>
-      <c r="I60" s="55">
+        <v>112</v>
+      </c>
+      <c r="H60" s="53">
+        <v>4.2</v>
+      </c>
+      <c r="I60" s="54">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3335,73 +3376,73 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B61" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C61" s="40" t="s">
+    <row r="61" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="B61" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="D61" s="32">
-        <v>1803439</v>
-      </c>
-      <c r="E61" s="36" t="s">
-        <v>180</v>
-      </c>
-      <c r="F61" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G61" s="37" t="s">
-        <v>183</v>
+      <c r="D61" s="50">
+        <v>1803426</v>
+      </c>
+      <c r="E61" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="F61" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="G61" s="52" t="s">
+        <v>54</v>
       </c>
       <c r="H61" s="38">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="I61" s="55">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="J61" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="B62" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C62" s="40" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="B62" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="D62" s="32">
-        <v>1745904</v>
-      </c>
-      <c r="E62" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="F62" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G62" s="37" t="s">
-        <v>182</v>
+      <c r="D62" s="50">
+        <v>1745894</v>
+      </c>
+      <c r="E62" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="F62" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="G62" s="52" t="s">
+        <v>57</v>
       </c>
       <c r="H62" s="38">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="I62" s="55">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="J62" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
         <v>59</v>
       </c>
@@ -3412,29 +3453,29 @@
         <v>7</v>
       </c>
       <c r="D63" s="32">
-        <v>1803442</v>
+        <v>1803439</v>
       </c>
       <c r="E63" s="36" t="s">
-        <v>62</v>
+        <v>175</v>
       </c>
       <c r="F63" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G63" s="37" t="s">
-        <v>61</v>
+        <v>178</v>
       </c>
       <c r="H63" s="38">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="I63" s="55">
         <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>0.9</v>
       </c>
       <c r="J63" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="17" t="s">
         <v>60</v>
       </c>
@@ -3445,31 +3486,31 @@
         <v>7</v>
       </c>
       <c r="D64" s="32">
-        <v>1745917</v>
+        <v>1745904</v>
       </c>
       <c r="E64" s="36" t="s">
-        <v>63</v>
+        <v>176</v>
       </c>
       <c r="F64" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G64" s="37" t="s">
-        <v>64</v>
+        <v>177</v>
       </c>
       <c r="H64" s="38">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="I64" s="55">
         <f t="shared" si="0"/>
-        <v>10.199999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="J64" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="17" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B65" s="31" t="s">
         <v>6</v>
@@ -3478,31 +3519,31 @@
         <v>7</v>
       </c>
       <c r="D65" s="32">
-        <v>1803468</v>
-      </c>
-      <c r="E65" s="63" t="s">
-        <v>67</v>
+        <v>1803442</v>
+      </c>
+      <c r="E65" s="36" t="s">
+        <v>62</v>
       </c>
       <c r="F65" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G65" s="37" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="H65" s="38">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="I65" s="55">
         <f t="shared" si="0"/>
-        <v>5.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="J65" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="17" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B66" s="31" t="s">
         <v>6</v>
@@ -3511,55 +3552,121 @@
         <v>7</v>
       </c>
       <c r="D66" s="32">
-        <v>1748011</v>
-      </c>
-      <c r="E66" s="63" t="s">
-        <v>68</v>
+        <v>1745917</v>
+      </c>
+      <c r="E66" s="36" t="s">
+        <v>63</v>
       </c>
       <c r="F66" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G66" s="37" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H66" s="38">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="I66" s="55">
         <f t="shared" si="0"/>
-        <v>16.5</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="J66" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="27"/>
-      <c r="B67" s="28"/>
-      <c r="G67" s="29"/>
-      <c r="H67" s="25"/>
-      <c r="I67" s="25">
-        <f>SUM(I9:I66)</f>
-        <v>234.1999999999999</v>
-      </c>
-      <c r="J67" s="26" t="s">
+    <row r="67" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B67" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" s="32">
+        <v>1803468</v>
+      </c>
+      <c r="E67" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="F67" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G67" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="H67" s="38">
+        <v>1.8</v>
+      </c>
+      <c r="I67" s="55">
+        <f t="shared" si="0"/>
+        <v>5.4</v>
+      </c>
+      <c r="J67" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B68" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" s="32">
+        <v>1748011</v>
+      </c>
+      <c r="E68" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="F68" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G68" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="H68" s="38">
+        <v>5.5</v>
+      </c>
+      <c r="I68" s="55">
+        <f t="shared" si="0"/>
+        <v>16.5</v>
+      </c>
+      <c r="J68" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="27"/>
+      <c r="B69" s="28"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="25"/>
+      <c r="I69" s="25">
+        <f>SUM(I9:I68)</f>
+        <v>237.6999999999999</v>
+      </c>
+      <c r="J69" s="26" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="6"/>
-      <c r="B68" s="7"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
-      <c r="G68" s="7"/>
-      <c r="H68" s="22"/>
-      <c r="I68" s="22"/>
-      <c r="J68" s="18"/>
+    <row r="70" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="6"/>
+      <c r="B70" s="7"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
+      <c r="G70" s="7"/>
+      <c r="H70" s="22"/>
+      <c r="I70" s="22"/>
+      <c r="J70" s="18"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:J68" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A5:J70" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="12">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A5:A6"/>
@@ -3575,7 +3682,7 @@
     <mergeCell ref="F5:F6"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
-  <conditionalFormatting sqref="J9:J66">
+  <conditionalFormatting sqref="J9:J68">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
